--- a/performance_data/test/metrics.xlsx
+++ b/performance_data/test/metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,21 +469,6 @@
           <t>rmse_vcell_spme_plus_blend</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>rmse_vcell_spme_plus_0p</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>rmse_vcell_spme_plus_0p_Ds</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>rmse_vcell_spme_plus_1p</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -503,28 +488,19 @@
         <v>19.04687556779734</v>
       </c>
       <c r="E2" t="n">
-        <v>2.191408878469329</v>
+        <v>3.995193148150587</v>
       </c>
       <c r="F2" t="n">
-        <v>3.723199925198482</v>
+        <v>4.138601976018851</v>
       </c>
       <c r="G2" t="n">
-        <v>2.240496024506036</v>
+        <v>2.135919650240949</v>
       </c>
       <c r="H2" t="n">
-        <v>4.959971885648662</v>
+        <v>4.972730706939338</v>
       </c>
       <c r="I2" t="n">
-        <v>2.018809566246423</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.108803017596853</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.554578172257328</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.048754114451659</v>
+        <v>2.9165255493968</v>
       </c>
     </row>
     <row r="3">
@@ -545,28 +521,19 @@
         <v>5.113970780343259</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5438618292784707</v>
+        <v>0.6736243600678498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.529001623812158</v>
+        <v>0.5567419984606135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5134182959277597</v>
+        <v>0.5100708401845239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8783755549591661</v>
+        <v>0.8370117601836291</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5300274493789259</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5091965176069345</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.2289538171271329</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.5067760701749426</v>
+        <v>0.5739400300625894</v>
       </c>
     </row>
     <row r="4">
@@ -587,28 +554,19 @@
         <v>4.899344001093768</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5567844900526795</v>
+        <v>1.038979576974992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5284147797719304</v>
+        <v>0.5242685968419705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5134671720732807</v>
+        <v>0.5544638352141662</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8757020281433711</v>
+        <v>1.689959351666321</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5435044732910936</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5544306730907463</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2763061528231558</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.5506382533896588</v>
+        <v>0.684087439788176</v>
       </c>
     </row>
     <row r="5">
@@ -629,28 +587,19 @@
         <v>17.57097444678893</v>
       </c>
       <c r="E5" t="n">
-        <v>8.653347471594492</v>
+        <v>13.43391381075187</v>
       </c>
       <c r="F5" t="n">
-        <v>4.872202866100945</v>
+        <v>4.945527791296143</v>
       </c>
       <c r="G5" t="n">
-        <v>5.872808886537968</v>
+        <v>6.197050086785267</v>
       </c>
       <c r="H5" t="n">
-        <v>9.001675554556774</v>
+        <v>22.83631848573129</v>
       </c>
       <c r="I5" t="n">
-        <v>6.551787255914521</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.24634375959941</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.392373379134717</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.189602977674725</v>
+        <v>8.086941263022634</v>
       </c>
     </row>
     <row r="6">
@@ -671,28 +620,19 @@
         <v>10.5557107833724</v>
       </c>
       <c r="E6" t="n">
-        <v>1.691283808759753</v>
+        <v>2.284571994658712</v>
       </c>
       <c r="F6" t="n">
-        <v>2.049497019531409</v>
+        <v>1.947205323854782</v>
       </c>
       <c r="G6" t="n">
-        <v>1.549484079709819</v>
+        <v>1.689836623265633</v>
       </c>
       <c r="H6" t="n">
-        <v>2.622146414109439</v>
+        <v>2.642018458263792</v>
       </c>
       <c r="I6" t="n">
-        <v>1.261162313156348</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.628628755786461</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.125954798191849</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.549727536060242</v>
+        <v>1.974294314246359</v>
       </c>
     </row>
     <row r="7">
@@ -713,28 +653,19 @@
         <v>9.849233146266807</v>
       </c>
       <c r="E7" t="n">
-        <v>3.49484234672112</v>
+        <v>3.173060873225161</v>
       </c>
       <c r="F7" t="n">
-        <v>2.093742568489095</v>
+        <v>1.897335763364106</v>
       </c>
       <c r="G7" t="n">
-        <v>1.803362044601773</v>
+        <v>1.964450190687178</v>
       </c>
       <c r="H7" t="n">
-        <v>1.981501653364203</v>
+        <v>4.619810291198466</v>
       </c>
       <c r="I7" t="n">
-        <v>2.040691893168462</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.931977165633645</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.346609246110586</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.874224819289383</v>
+        <v>2.330402028382681</v>
       </c>
     </row>
     <row r="8">
@@ -755,28 +686,19 @@
         <v>14.71422591906435</v>
       </c>
       <c r="E8" t="n">
-        <v>7.268883891616635</v>
+        <v>5.072578430145408</v>
       </c>
       <c r="F8" t="n">
-        <v>4.760128529344402</v>
+        <v>4.359338052911863</v>
       </c>
       <c r="G8" t="n">
-        <v>4.132015920494424</v>
+        <v>4.073403465771374</v>
       </c>
       <c r="H8" t="n">
-        <v>5.631632891632743</v>
+        <v>7.567635600512189</v>
       </c>
       <c r="I8" t="n">
-        <v>5.331217154108328</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.122725312465573</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.855960947738637</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4.176608476502053</v>
+        <v>4.205238546527524</v>
       </c>
     </row>
   </sheetData>
